--- a/INSTANCES/instances_xlsx/A_MTN_1/84FL_3A_19.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_1/84FL_3A_19.xlsx
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3403,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
